--- a/VerveStacks_ZWE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZWE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZWE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3926D625-B0AE-4D85-862E-F38ED53C8549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B06B3BB6-2F51-46B4-82CF-E58DCA841602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ZWE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZWE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZWE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B06B3BB6-2F51-46B4-82CF-E58DCA841602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{508D2A4B-FACE-4135-9C4F-14DB9C4D7600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>

--- a/VerveStacks_ZWE/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZWE/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZWE\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{508D2A4B-FACE-4135-9C4F-14DB9C4D7600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC62ECC3-25CB-4A89-BE71-FE4557F9F62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
